--- a/suivi_comptes_vierge.xlsx
+++ b/suivi_comptes_vierge.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
   <si>
     <t xml:space="preserve">Synthèse mensuelle</t>
   </si>
@@ -3812,13 +3812,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3849,6 +3852,15 @@
       </c>
       <c r="F4" s="4" t="s">
         <v>67</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3861,6 +3873,9 @@
         <f aca="false">IF(A5="","",IFERROR(E5/INDEX(Paramètres!$E$4:$E$7,MATCH(D5,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
@@ -3872,6 +3887,9 @@
         <f aca="false">IF(A6="","",IFERROR(E6/INDEX(Paramètres!$E$4:$E$7,MATCH(D6,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
@@ -3883,6 +3901,9 @@
         <f aca="false">IF(A7="","",IFERROR(E7/INDEX(Paramètres!$E$4:$E$7,MATCH(D7,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
@@ -3894,6 +3915,9 @@
         <f aca="false">IF(A8="","",IFERROR(E8/INDEX(Paramètres!$E$4:$E$7,MATCH(D8,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13"/>
@@ -3905,6 +3929,9 @@
         <f aca="false">IF(A9="","",IFERROR(E9/INDEX(Paramètres!$E$4:$E$7,MATCH(D9,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13"/>
@@ -3916,6 +3943,9 @@
         <f aca="false">IF(A10="","",IFERROR(E10/INDEX(Paramètres!$E$4:$E$7,MATCH(D10,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13"/>
@@ -3927,6 +3957,9 @@
         <f aca="false">IF(A11="","",IFERROR(E11/INDEX(Paramètres!$E$4:$E$7,MATCH(D11,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13"/>
@@ -3938,6 +3971,9 @@
         <f aca="false">IF(A12="","",IFERROR(E12/INDEX(Paramètres!$E$4:$E$7,MATCH(D12,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13"/>
@@ -3949,6 +3985,9 @@
         <f aca="false">IF(A13="","",IFERROR(E13/INDEX(Paramètres!$E$4:$E$7,MATCH(D13,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13"/>
@@ -3960,6 +3999,9 @@
         <f aca="false">IF(A14="","",IFERROR(E14/INDEX(Paramètres!$E$4:$E$7,MATCH(D14,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13"/>
@@ -3971,6 +4013,9 @@
         <f aca="false">IF(A15="","",IFERROR(E15/INDEX(Paramètres!$E$4:$E$7,MATCH(D15,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13"/>
@@ -3982,6 +4027,9 @@
         <f aca="false">IF(A16="","",IFERROR(E16/INDEX(Paramètres!$E$4:$E$7,MATCH(D16,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13"/>
@@ -3993,6 +4041,9 @@
         <f aca="false">IF(A17="","",IFERROR(E17/INDEX(Paramètres!$E$4:$E$7,MATCH(D17,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13"/>
@@ -4004,6 +4055,9 @@
         <f aca="false">IF(A18="","",IFERROR(E18/INDEX(Paramètres!$E$4:$E$7,MATCH(D18,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13"/>
@@ -4015,6 +4069,9 @@
         <f aca="false">IF(A19="","",IFERROR(E19/INDEX(Paramètres!$E$4:$E$7,MATCH(D19,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13"/>
@@ -4026,6 +4083,9 @@
         <f aca="false">IF(A20="","",IFERROR(E20/INDEX(Paramètres!$E$4:$E$7,MATCH(D20,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13"/>
@@ -4037,6 +4097,9 @@
         <f aca="false">IF(A21="","",IFERROR(E21/INDEX(Paramètres!$E$4:$E$7,MATCH(D21,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13"/>
@@ -4048,6 +4111,9 @@
         <f aca="false">IF(A22="","",IFERROR(E22/INDEX(Paramètres!$E$4:$E$7,MATCH(D22,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13"/>
@@ -4059,6 +4125,9 @@
         <f aca="false">IF(A23="","",IFERROR(E23/INDEX(Paramètres!$E$4:$E$7,MATCH(D23,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
@@ -4070,6 +4139,9 @@
         <f aca="false">IF(A24="","",IFERROR(E24/INDEX(Paramètres!$E$4:$E$7,MATCH(D24,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13"/>
@@ -4081,6 +4153,9 @@
         <f aca="false">IF(A25="","",IFERROR(E25/INDEX(Paramètres!$E$4:$E$7,MATCH(D25,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13"/>
@@ -4092,6 +4167,9 @@
         <f aca="false">IF(A26="","",IFERROR(E26/INDEX(Paramètres!$E$4:$E$7,MATCH(D26,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13"/>
@@ -4103,6 +4181,9 @@
         <f aca="false">IF(A27="","",IFERROR(E27/INDEX(Paramètres!$E$4:$E$7,MATCH(D27,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13"/>
@@ -4114,6 +4195,9 @@
         <f aca="false">IF(A28="","",IFERROR(E28/INDEX(Paramètres!$E$4:$E$7,MATCH(D28,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13"/>
@@ -4125,6 +4209,9 @@
         <f aca="false">IF(A29="","",IFERROR(E29/INDEX(Paramètres!$E$4:$E$7,MATCH(D29,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13"/>
@@ -4136,6 +4223,9 @@
         <f aca="false">IF(A30="","",IFERROR(E30/INDEX(Paramètres!$E$4:$E$7,MATCH(D30,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13"/>
@@ -4147,6 +4237,9 @@
         <f aca="false">IF(A31="","",IFERROR(E31/INDEX(Paramètres!$E$4:$E$7,MATCH(D31,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13"/>
@@ -4158,6 +4251,9 @@
         <f aca="false">IF(A32="","",IFERROR(E32/INDEX(Paramètres!$E$4:$E$7,MATCH(D32,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13"/>
@@ -4169,6 +4265,9 @@
         <f aca="false">IF(A33="","",IFERROR(E33/INDEX(Paramètres!$E$4:$E$7,MATCH(D33,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13"/>
@@ -4180,6 +4279,9 @@
         <f aca="false">IF(A34="","",IFERROR(E34/INDEX(Paramètres!$E$4:$E$7,MATCH(D34,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13"/>
@@ -4191,6 +4293,9 @@
         <f aca="false">IF(A35="","",IFERROR(E35/INDEX(Paramètres!$E$4:$E$7,MATCH(D35,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13"/>
@@ -4202,6 +4307,9 @@
         <f aca="false">IF(A36="","",IFERROR(E36/INDEX(Paramètres!$E$4:$E$7,MATCH(D36,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13"/>
@@ -4213,6 +4321,9 @@
         <f aca="false">IF(A37="","",IFERROR(E37/INDEX(Paramètres!$E$4:$E$7,MATCH(D37,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13"/>
@@ -4224,6 +4335,9 @@
         <f aca="false">IF(A38="","",IFERROR(E38/INDEX(Paramètres!$E$4:$E$7,MATCH(D38,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13"/>
@@ -4235,6 +4349,9 @@
         <f aca="false">IF(A39="","",IFERROR(E39/INDEX(Paramètres!$E$4:$E$7,MATCH(D39,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13"/>
@@ -4246,6 +4363,9 @@
         <f aca="false">IF(A40="","",IFERROR(E40/INDEX(Paramètres!$E$4:$E$7,MATCH(D40,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13"/>
@@ -4257,6 +4377,9 @@
         <f aca="false">IF(A41="","",IFERROR(E41/INDEX(Paramètres!$E$4:$E$7,MATCH(D41,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13"/>
@@ -4268,6 +4391,9 @@
         <f aca="false">IF(A42="","",IFERROR(E42/INDEX(Paramètres!$E$4:$E$7,MATCH(D42,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13"/>
@@ -4279,6 +4405,9 @@
         <f aca="false">IF(A43="","",IFERROR(E43/INDEX(Paramètres!$E$4:$E$7,MATCH(D43,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13"/>
@@ -4290,6 +4419,9 @@
         <f aca="false">IF(A44="","",IFERROR(E44/INDEX(Paramètres!$E$4:$E$7,MATCH(D44,Paramètres!$D$4:$D$7,0)),0))</f>
         <v/>
       </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
@@ -4301,9 +4433,17 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D44" type="list">
       <formula1>"Mensuelle,Trimestrielle,Semestrielle,Annuelle"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H44" type="list">
+      <formula1>Comptes!$A$5:$A$14</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G44" type="list">
+      <formula1>"Prélèvement,Carte,Chèque,Espèces,Virement"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B44" type="list">

--- a/suivi_comptes_vierge.xlsx
+++ b/suivi_comptes_vierge.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t xml:space="preserve">Synthèse mensuelle</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t xml:space="preserve">Alimente la ligne « Provision imprévus » de l'onglet Charges (réparties 50/50, sur le compte joint indiqué).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version du modèle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voir MIGRATION.md pour migrer un fichier d'une version à l'autre.</t>
   </si>
   <si>
     <t xml:space="preserve">Comptes bancaires</t>
@@ -1612,7 +1621,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1794,6 +1803,19 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1833,26 +1855,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1956,50 +1978,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M4" s="4" t="str">
         <f aca="false">"Part "&amp;Paramètres!$B$4&amp;" (€/mois)"</f>
@@ -3412,7 +3434,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">SUM(F5:F54)</f>
@@ -3479,17 +3501,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>18</v>
@@ -3498,19 +3520,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3775,7 +3797,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F25" s="9" t="n">
         <f aca="false">SUM(F5:F24)</f>
@@ -3826,41 +3848,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4425,7 +4447,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F45" s="9" t="n">
         <f aca="false">SUM(F5:F44)</f>
@@ -4434,20 +4456,20 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D44" type="list">
-      <formula1>"Mensuelle,Trimestrielle,Semestrielle,Annuelle"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G44" type="list">
+      <formula1>"Prélèvement,Carte,Chèque,Espèces,Virement"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H44" type="list">
       <formula1>Comptes!$A$5:$A$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G44" type="list">
-      <formula1>"Prélèvement,Carte,Chèque,Espèces,Virement"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B44" type="list">
+      <formula1>Paramètres!$B$4:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B44" type="list">
-      <formula1>Paramètres!$B$4:$B$5</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D44" type="list">
+      <formula1>"Mensuelle,Trimestrielle,Semestrielle,Annuelle"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4477,17 +4499,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">SUMIFS(Charges!$F$5:$F$54,Charges!$B$5:$B$54,"Imprévus")</f>
@@ -4496,13 +4518,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0</v>
@@ -4510,7 +4532,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="true">IF(B5="",0,MAX(0,(YEAR(TODAY())-YEAR(B5))*12+MONTH(TODAY())-MONTH(B5)+1))</f>
@@ -4519,7 +4541,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">B6+B4*B7</f>
@@ -4528,7 +4550,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">SUM(C13:C62)</f>
@@ -4537,7 +4559,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">B8-B9</f>
@@ -4546,21 +4568,21 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/suivi_comptes_vierge.xlsx
+++ b/suivi_comptes_vierge.xlsx
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t xml:space="preserve">Synthèse mensuelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Tout est calculé à partir des onglets Charges, Revenus et Comptes. Ne rien saisir ici.</t>
+    <t xml:space="preserve">Tout est calculé à partir des autres onglets (Paramètres, Comptes, Charges, Revenus, Charges perso). Ne rien saisir ici.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Par personne</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : un compte joint à solde 0 est équilibré. Un compte perso à solde positif = reste à vivre ; négatif = salaire insuffisant. Les aides sont réparties sur les deux personnes au prorata de leurs parts de charges (hypothèse).</t>
+    <t xml:space="preserve">Lecture : un compte joint à solde 0 est équilibré. Un compte perso à solde positif = reste après charges communes (avant charges perso et épargne perso, voir tableau 1) ; négatif = salaire insuffisant. Un compte d'épargne affiche les virements reçus ce mois. Les aides sont réparties sur les deux personnes au prorata de leurs parts de charges (hypothèse).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Charges communes : fixe vs variable (mensuel)</t>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">Part de la Personne 1 dans les salaires (pour « Prorata salaires »)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hypothèse : 50 % si aucun salaire n'est saisi.</t>
+    <t xml:space="preserve">Hypothèse : 50 % si aucun salaire n'est saisi. Le prénom des salaires (onglet Revenus) doit être identique à celui saisi plus haut.</t>
   </si>
   <si>
     <t xml:space="preserve">Modes de répartition possibles : 50/50 · Prorata salaires · Personne 1 seul · Personne 2 seul</t>
@@ -181,7 +181,7 @@
     <t xml:space="preserve">Pourcentage</t>
   </si>
   <si>
-    <t xml:space="preserve">Épargne perso : pourcentage du reste (si Pourcentage)</t>
+    <t xml:space="preserve">Épargne perso : pourcentage du reste après charges perso (si Pourcentage)</t>
   </si>
   <si>
     <t xml:space="preserve">Épargne perso : montant €/mois (si Montant)</t>
@@ -193,13 +193,13 @@
     <t xml:space="preserve">Provision imprévus (% des salaires du foyer)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alimente la ligne « Provision imprévus » de l'onglet Charges (réparties 50/50, sur le compte joint indiqué).</t>
+    <t xml:space="preserve">Le montant de la ligne « Provision imprévus » de l'onglet Charges vaut ce pourcentage × les salaires mensuels du foyer. Les comptes (débité et destinataire) et la répartition de cette ligne sont à régler dans Charges.</t>
   </si>
   <si>
     <t xml:space="preserve">Version du modèle</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0.0</t>
+    <t xml:space="preserve">1.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">Voir MIGRATION.md pour migrer un fichier d'une version à l'autre.</t>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">Comptes bancaires</t>
   </si>
   <si>
-    <t xml:space="preserve">Paramétrez ici vos comptes (10 lignes). Le nom saisi ici alimente les listes déroulantes des autres onglets.</t>
+    <t xml:space="preserve">Paramétrez ici vos comptes (10 lignes). Le nom saisi ici alimente les listes déroulantes des autres onglets. Si vous renommez un compte, corrigez-le aussi dans les lignes déjà saisies.</t>
   </si>
   <si>
     <t xml:space="preserve">Nom du compte</t>
@@ -259,13 +259,28 @@
     <t xml:space="preserve">Part P1 (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Provision imprévus (% des salaires)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprévus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50/50</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL mensuel</t>
   </si>
   <si>
     <t xml:space="preserve">Revenus et aides</t>
   </si>
   <si>
-    <t xml:space="preserve">Salaires (arrivent sur le compte de chacun) et aides type CAF (peuvent arriver sur un compte joint). 20 lignes.</t>
+    <t xml:space="preserve">Salaires (arrivent sur le compte de chacun) et aides type CAF (peuvent arriver sur un compte joint). 20 lignes. Colonne Personne : prénom identique à Paramètres (obligatoire pour un salaire), ou « Commun ».</t>
   </si>
   <si>
     <t xml:space="preserve">Compte de réception</t>
@@ -283,7 +298,7 @@
     <t xml:space="preserve">Notez chaque dépense imprévue ici (date, libellé, montant). Le solde de la provision se met à jour tout seul.</t>
   </si>
   <si>
-    <t xml:space="preserve">Provision mensuelle (ligne « Imprévus » de Charges)</t>
+    <t xml:space="preserve">Provision mensuelle (somme des lignes de catégorie « Imprévus » dans Charges)</t>
   </si>
   <si>
     <t xml:space="preserve">Début du suivi (1er du mois)</t>
@@ -501,7 +516,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -583,6 +598,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2033,31 +2052,46 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="6" t="str">
+      <c r="A5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <f aca="false">Paramètres!$B$22*SUMIFS(Revenus!$F$5:$F$24,Revenus!$B$5:$B$24,"Salaire")</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <f aca="false">IF(A5="","",IFERROR(E5/INDEX(Paramètres!$E$4:$E$7,MATCH(D5,Paramètres!$D$4:$D$7,0)),0))</f>
-        <v/>
-      </c>
-      <c r="G5" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="7" t="str">
+      <c r="K5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="7" t="n">
         <f aca="false">IF(A5="","",IF(K5="50/50",0.5,IF(K5="Prorata salaires",Paramètres!$B$9,IF(K5="Personne 1 seul",1,IF(K5="Personne 2 seul",0,0.5)))))</f>
-        <v/>
-      </c>
-      <c r="M5" s="6" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="6" t="n">
         <f aca="false">IF(A5="","",F5*L5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="n">
         <f aca="false">IF(A5="","",F5-M5)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3433,8 +3467,8 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>77</v>
+      <c r="A55" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">SUM(F5:F54)</f>
@@ -3501,12 +3535,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3529,7 +3563,7 @@
         <v>70</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>74</v>
@@ -3796,8 +3830,8 @@
       <c r="H24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
-        <v>77</v>
+      <c r="A25" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="F25" s="9" t="n">
         <f aca="false">SUM(F5:F24)</f>
@@ -3848,12 +3882,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4446,8 +4480,8 @@
       <c r="I44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21" t="s">
-        <v>77</v>
+      <c r="A45" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="F45" s="9" t="n">
         <f aca="false">SUM(F5:F44)</f>
@@ -4499,17 +4533,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>85</v>
+      <c r="A4" s="23" t="s">
+        <v>90</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">SUMIFS(Charges!$F$5:$F$54,Charges!$B$5:$B$54,"Imprévus")</f>
@@ -4517,31 +4551,31 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="23"/>
+      <c r="A5" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>87</v>
+      <c r="A6" s="23" t="s">
+        <v>92</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="24" t="n">
+      <c r="A7" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="true">IF(B5="",0,MAX(0,(YEAR(TODAY())-YEAR(B5))*12+MONTH(TODAY())-MONTH(B5)+1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>89</v>
+      <c r="A8" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">B6+B4*B7</f>
@@ -4549,8 +4583,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>90</v>
+      <c r="A9" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">SUM(C13:C62)</f>
@@ -4559,7 +4593,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">B8-B9</f>
@@ -4568,319 +4602,319 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="13"/>
       <c r="C13" s="18"/>
       <c r="D13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="13"/>
       <c r="C14" s="18"/>
       <c r="D14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="13"/>
       <c r="C15" s="18"/>
       <c r="D15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="13"/>
       <c r="C16" s="18"/>
       <c r="D16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="13"/>
       <c r="C17" s="18"/>
       <c r="D17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="13"/>
       <c r="C18" s="18"/>
       <c r="D18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="13"/>
       <c r="C19" s="18"/>
       <c r="D19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="13"/>
       <c r="C20" s="18"/>
       <c r="D20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="13"/>
       <c r="C21" s="18"/>
       <c r="D21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="13"/>
       <c r="C22" s="18"/>
       <c r="D22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="13"/>
       <c r="C23" s="18"/>
       <c r="D23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="13"/>
       <c r="C24" s="18"/>
       <c r="D24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="13"/>
       <c r="C25" s="18"/>
       <c r="D25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="13"/>
       <c r="C26" s="18"/>
       <c r="D26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="13"/>
       <c r="C27" s="18"/>
       <c r="D27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="13"/>
       <c r="C28" s="18"/>
       <c r="D28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="13"/>
       <c r="C29" s="18"/>
       <c r="D29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="13"/>
       <c r="C30" s="18"/>
       <c r="D30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="13"/>
       <c r="C31" s="18"/>
       <c r="D31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="13"/>
       <c r="C32" s="18"/>
       <c r="D32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="13"/>
       <c r="C33" s="18"/>
       <c r="D33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23"/>
+      <c r="A34" s="24"/>
       <c r="B34" s="13"/>
       <c r="C34" s="18"/>
       <c r="D34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="13"/>
       <c r="C35" s="18"/>
       <c r="D35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="13"/>
       <c r="C36" s="18"/>
       <c r="D36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="13"/>
       <c r="C37" s="18"/>
       <c r="D37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
+      <c r="A38" s="24"/>
       <c r="B38" s="13"/>
       <c r="C38" s="18"/>
       <c r="D38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="13"/>
       <c r="C39" s="18"/>
       <c r="D39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
+      <c r="A40" s="24"/>
       <c r="B40" s="13"/>
       <c r="C40" s="18"/>
       <c r="D40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23"/>
+      <c r="A41" s="24"/>
       <c r="B41" s="13"/>
       <c r="C41" s="18"/>
       <c r="D41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23"/>
+      <c r="A42" s="24"/>
       <c r="B42" s="13"/>
       <c r="C42" s="18"/>
       <c r="D42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23"/>
+      <c r="A43" s="24"/>
       <c r="B43" s="13"/>
       <c r="C43" s="18"/>
       <c r="D43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23"/>
+      <c r="A44" s="24"/>
       <c r="B44" s="13"/>
       <c r="C44" s="18"/>
       <c r="D44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23"/>
+      <c r="A45" s="24"/>
       <c r="B45" s="13"/>
       <c r="C45" s="18"/>
       <c r="D45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="13"/>
       <c r="C46" s="18"/>
       <c r="D46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23"/>
+      <c r="A47" s="24"/>
       <c r="B47" s="13"/>
       <c r="C47" s="18"/>
       <c r="D47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="13"/>
       <c r="C48" s="18"/>
       <c r="D48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="13"/>
       <c r="C49" s="18"/>
       <c r="D49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="13"/>
       <c r="C50" s="18"/>
       <c r="D50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="13"/>
       <c r="C51" s="18"/>
       <c r="D51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="13"/>
       <c r="C52" s="18"/>
       <c r="D52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="13"/>
       <c r="C53" s="18"/>
       <c r="D53" s="13"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="13"/>
       <c r="C54" s="18"/>
       <c r="D54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="23"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="13"/>
       <c r="C55" s="18"/>
       <c r="D55" s="13"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="23"/>
+      <c r="A56" s="24"/>
       <c r="B56" s="13"/>
       <c r="C56" s="18"/>
       <c r="D56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="23"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="13"/>
       <c r="C57" s="18"/>
       <c r="D57" s="13"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="23"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="13"/>
       <c r="C58" s="18"/>
       <c r="D58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="23"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="13"/>
       <c r="C59" s="18"/>
       <c r="D59" s="13"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="13"/>
       <c r="C60" s="18"/>
       <c r="D60" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="13"/>
       <c r="C61" s="18"/>
       <c r="D61" s="13"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="13"/>
       <c r="C62" s="18"/>
       <c r="D62" s="13"/>

--- a/suivi_comptes_vierge.xlsx
+++ b/suivi_comptes_vierge.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="104">
   <si>
     <t xml:space="preserve">Synthèse mensuelle</t>
   </si>
@@ -100,13 +100,19 @@
     <t xml:space="preserve">Participations versées (vers comptes joints)</t>
   </si>
   <si>
+    <t xml:space="preserve">Solde avant charges perso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charges perso &amp; épargne perso débitées</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solde mensuel prévisionnel</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : un compte joint à solde 0 est équilibré. Un compte perso à solde positif = reste après charges communes (avant charges perso et épargne perso, voir tableau 1) ; négatif = salaire insuffisant. Un compte d'épargne affiche les virements reçus ce mois. Les aides sont réparties sur les deux personnes au prorata de leurs parts de charges (hypothèse).</t>
+    <t xml:space="preserve">Lecture : un compte joint à solde 0 est équilibré. Un compte perso à solde positif = ce qu'il reste après charges communes, charges perso (détail ou forfait) et épargne perso, imputées à ce compte (compte débité de la ligne, sinon le compte perso) ; négatif = salaire insuffisant. Un compte d'épargne affiche les virements reçus ce mois. Les aides sont réparties sur les deux personnes au prorata de leurs parts de charges (hypothèse).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Charges communes : fixe vs variable (mensuel)</t>
@@ -199,7 +205,7 @@
     <t xml:space="preserve">Version du modèle</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0.1</t>
+    <t xml:space="preserve">1.1.0</t>
   </si>
   <si>
     <t xml:space="preserve">Voir MIGRATION.md pour migrer un fichier d'une version à l'autre.</t>
@@ -289,7 +295,10 @@
     <t xml:space="preserve">Charges personnelles (facultatif)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dépenses propres à chacun. Utilisé seulement si le mode « Détail » est choisi pour la personne dans Paramètres.</t>
+    <t xml:space="preserve">Dépenses propres à chacun. Utilisé seulement si le mode « Détail » est choisi pour la personne dans Paramètres. Compte débité : si vide, la dépense est imputée au compte perso de la personne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte imputé (calculé)</t>
   </si>
   <si>
     <t xml:space="preserve">Suivi des imprévus</t>
@@ -873,7 +882,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -883,7 +892,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1116,6 +1127,12 @@
       <c r="J12" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="K12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="str">
@@ -1158,6 +1175,14 @@
         <f aca="false">IF($A13="","",G13+D13+H13+IF(B13="Joint",E13+F13,0)-C13-I13)</f>
         <v/>
       </c>
+      <c r="K13" s="6" t="str">
+        <f aca="false">IF($A13="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A13)+IF(AND($A13=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A13=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A13=Paramètres!$B$6,$J$5,0)+IF($A13=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="6" t="str">
+        <f aca="false">IF($A13="","",J13-K13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="str">
@@ -1200,6 +1225,14 @@
         <f aca="false">IF($A14="","",G14+D14+H14+IF(B14="Joint",E14+F14,0)-C14-I14)</f>
         <v/>
       </c>
+      <c r="K14" s="6" t="str">
+        <f aca="false">IF($A14="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A14)+IF(AND($A14=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A14=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A14=Paramètres!$B$6,$J$5,0)+IF($A14=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="6" t="str">
+        <f aca="false">IF($A14="","",J14-K14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="str">
@@ -1242,6 +1275,14 @@
         <f aca="false">IF($A15="","",G15+D15+H15+IF(B15="Joint",E15+F15,0)-C15-I15)</f>
         <v/>
       </c>
+      <c r="K15" s="6" t="str">
+        <f aca="false">IF($A15="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A15)+IF(AND($A15=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A15=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A15=Paramètres!$B$6,$J$5,0)+IF($A15=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="6" t="str">
+        <f aca="false">IF($A15="","",J15-K15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="str">
@@ -1284,6 +1325,14 @@
         <f aca="false">IF($A16="","",G16+D16+H16+IF(B16="Joint",E16+F16,0)-C16-I16)</f>
         <v/>
       </c>
+      <c r="K16" s="6" t="str">
+        <f aca="false">IF($A16="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A16)+IF(AND($A16=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A16=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A16=Paramètres!$B$6,$J$5,0)+IF($A16=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="6" t="str">
+        <f aca="false">IF($A16="","",J16-K16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="str">
@@ -1326,6 +1375,14 @@
         <f aca="false">IF($A17="","",G17+D17+H17+IF(B17="Joint",E17+F17,0)-C17-I17)</f>
         <v/>
       </c>
+      <c r="K17" s="6" t="str">
+        <f aca="false">IF($A17="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A17)+IF(AND($A17=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A17=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A17=Paramètres!$B$6,$J$5,0)+IF($A17=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="6" t="str">
+        <f aca="false">IF($A17="","",J17-K17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="str">
@@ -1368,6 +1425,14 @@
         <f aca="false">IF($A18="","",G18+D18+H18+IF(B18="Joint",E18+F18,0)-C18-I18)</f>
         <v/>
       </c>
+      <c r="K18" s="6" t="str">
+        <f aca="false">IF($A18="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A18)+IF(AND($A18=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A18=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A18=Paramètres!$B$6,$J$5,0)+IF($A18=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="6" t="str">
+        <f aca="false">IF($A18="","",J18-K18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="str">
@@ -1410,6 +1475,14 @@
         <f aca="false">IF($A19="","",G19+D19+H19+IF(B19="Joint",E19+F19,0)-C19-I19)</f>
         <v/>
       </c>
+      <c r="K19" s="6" t="str">
+        <f aca="false">IF($A19="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A19)+IF(AND($A19=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A19=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A19=Paramètres!$B$6,$J$5,0)+IF($A19=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="6" t="str">
+        <f aca="false">IF($A19="","",J19-K19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="str">
@@ -1452,6 +1525,14 @@
         <f aca="false">IF($A20="","",G20+D20+H20+IF(B20="Joint",E20+F20,0)-C20-I20)</f>
         <v/>
       </c>
+      <c r="K20" s="6" t="str">
+        <f aca="false">IF($A20="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A20)+IF(AND($A20=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A20=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A20=Paramètres!$B$6,$J$5,0)+IF($A20=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="6" t="str">
+        <f aca="false">IF($A20="","",J20-K20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="str">
@@ -1494,6 +1575,14 @@
         <f aca="false">IF($A21="","",G21+D21+H21+IF(B21="Joint",E21+F21,0)-C21-I21)</f>
         <v/>
       </c>
+      <c r="K21" s="6" t="str">
+        <f aca="false">IF($A21="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A21)+IF(AND($A21=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A21=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A21=Paramètres!$B$6,$J$5,0)+IF($A21=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="6" t="str">
+        <f aca="false">IF($A21="","",J21-K21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="str">
@@ -1536,10 +1625,18 @@
         <f aca="false">IF($A22="","",G22+D22+H22+IF(B22="Joint",E22+F22,0)-C22-I22)</f>
         <v/>
       </c>
+      <c r="K22" s="6" t="str">
+        <f aca="false">IF($A22="","",SUMIFS('Charges perso'!$F$5:$F$44,'Charges perso'!$J$5:$J$44,$A22)+IF(AND($A22=Paramètres!$B$6,Paramètres!$B$15="Forfait"),Paramètres!$B$16,0)+IF(AND($A22=Paramètres!$B$7,Paramètres!$C$15="Forfait"),Paramètres!$C$16,0)+IF($A22=Paramètres!$B$6,$J$5,0)+IF($A22=Paramètres!$B$7,$J$6,0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="6" t="str">
+        <f aca="false">IF($A22="","",J22-K22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="n">
@@ -1574,20 +1671,28 @@
         <f aca="false">SUM(J13:J22)</f>
         <v>0</v>
       </c>
+      <c r="K23" s="9" t="n">
+        <f aca="false">SUM(K13:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <f aca="false">SUM(L13:L22)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="6" t="n">
         <f aca="false">SUMIFS(Charges!$F$5:$F$54,Charges!$C$5:$C$54,"Fixe")</f>
@@ -1600,7 +1705,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29" s="6" t="n">
         <f aca="false">SUMIFS(Charges!$F$5:$F$54,Charges!$C$5:$C$54,"Variable")</f>
@@ -1613,7 +1718,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="9" t="n">
         <f aca="false">B28+B29</f>
@@ -1651,31 +1756,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D3" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>1</v>
@@ -1683,13 +1788,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3</v>
@@ -1697,11 +1802,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="13"/>
       <c r="D6" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
@@ -1709,11 +1814,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="13"/>
       <c r="D7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>12</v>
@@ -1721,7 +1826,7 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(SUMIFS(Revenus!$F$5:$F$24,Revenus!$B$5:$B$24,"Salaire",Revenus!$C$5:$C$24,$B$4)/SUMIFS(Revenus!$F$5:$F$24,Revenus!$B$5:$B$24,"Salaire"),0.5)</f>
@@ -1730,17 +1835,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="16" t="str">
         <f aca="false">$B$4</f>
@@ -1753,18 +1858,18 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>0</v>
@@ -1775,18 +1880,18 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>0</v>
@@ -1797,7 +1902,7 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>0</v>
@@ -1808,12 +1913,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>0</v>
@@ -1821,20 +1926,20 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1874,26 +1979,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,50 +2102,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M4" s="4" t="str">
         <f aca="false">"Part "&amp;Paramètres!$B$4&amp;" (€/mois)"</f>
@@ -2053,16 +2158,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">Paramètres!$B$22*SUMIFS(Revenus!$F$5:$F$24,Revenus!$B$5:$B$24,"Salaire")</f>
@@ -2073,13 +2178,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L5" s="7" t="n">
         <f aca="false">IF(A5="","",IF(K5="50/50",0.5,IF(K5="Prorata salaires",Paramètres!$B$9,IF(K5="Personne 1 seul",1,IF(K5="Personne 2 seul",0,0.5)))))</f>
@@ -3468,7 +3573,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">SUM(F5:F54)</f>
@@ -3535,17 +3640,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>18</v>
@@ -3554,19 +3659,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3831,7 +3936,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F25" s="9" t="n">
         <f aca="false">SUM(F5:F24)</f>
@@ -3868,7 +3973,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -3878,45 +3983,49 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,6 +4041,10 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
+      <c r="J5" s="5" t="str">
+        <f aca="false">IF(OR($A5="",AND($B5&lt;&gt;Paramètres!$B$4,$B5&lt;&gt;Paramètres!$B$5)),"",IF(IF($B5=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H5&lt;&gt;"",$H5,IF($B5=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
@@ -3946,6 +4059,10 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
+      <c r="J6" s="5" t="str">
+        <f aca="false">IF(OR($A6="",AND($B6&lt;&gt;Paramètres!$B$4,$B6&lt;&gt;Paramètres!$B$5)),"",IF(IF($B6=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H6&lt;&gt;"",$H6,IF($B6=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
@@ -3960,6 +4077,10 @@
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
+      <c r="J7" s="5" t="str">
+        <f aca="false">IF(OR($A7="",AND($B7&lt;&gt;Paramètres!$B$4,$B7&lt;&gt;Paramètres!$B$5)),"",IF(IF($B7=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H7&lt;&gt;"",$H7,IF($B7=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
@@ -3974,6 +4095,10 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
+      <c r="J8" s="5" t="str">
+        <f aca="false">IF(OR($A8="",AND($B8&lt;&gt;Paramètres!$B$4,$B8&lt;&gt;Paramètres!$B$5)),"",IF(IF($B8=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H8&lt;&gt;"",$H8,IF($B8=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13"/>
@@ -3988,6 +4113,10 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
+      <c r="J9" s="5" t="str">
+        <f aca="false">IF(OR($A9="",AND($B9&lt;&gt;Paramètres!$B$4,$B9&lt;&gt;Paramètres!$B$5)),"",IF(IF($B9=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H9&lt;&gt;"",$H9,IF($B9=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13"/>
@@ -4002,6 +4131,10 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
+      <c r="J10" s="5" t="str">
+        <f aca="false">IF(OR($A10="",AND($B10&lt;&gt;Paramètres!$B$4,$B10&lt;&gt;Paramètres!$B$5)),"",IF(IF($B10=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H10&lt;&gt;"",$H10,IF($B10=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13"/>
@@ -4016,6 +4149,10 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
+      <c r="J11" s="5" t="str">
+        <f aca="false">IF(OR($A11="",AND($B11&lt;&gt;Paramètres!$B$4,$B11&lt;&gt;Paramètres!$B$5)),"",IF(IF($B11=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H11&lt;&gt;"",$H11,IF($B11=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13"/>
@@ -4030,6 +4167,10 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
+      <c r="J12" s="5" t="str">
+        <f aca="false">IF(OR($A12="",AND($B12&lt;&gt;Paramètres!$B$4,$B12&lt;&gt;Paramètres!$B$5)),"",IF(IF($B12=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H12&lt;&gt;"",$H12,IF($B12=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13"/>
@@ -4044,6 +4185,10 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
+      <c r="J13" s="5" t="str">
+        <f aca="false">IF(OR($A13="",AND($B13&lt;&gt;Paramètres!$B$4,$B13&lt;&gt;Paramètres!$B$5)),"",IF(IF($B13=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H13&lt;&gt;"",$H13,IF($B13=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13"/>
@@ -4058,6 +4203,10 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
+      <c r="J14" s="5" t="str">
+        <f aca="false">IF(OR($A14="",AND($B14&lt;&gt;Paramètres!$B$4,$B14&lt;&gt;Paramètres!$B$5)),"",IF(IF($B14=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H14&lt;&gt;"",$H14,IF($B14=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13"/>
@@ -4072,6 +4221,10 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
+      <c r="J15" s="5" t="str">
+        <f aca="false">IF(OR($A15="",AND($B15&lt;&gt;Paramètres!$B$4,$B15&lt;&gt;Paramètres!$B$5)),"",IF(IF($B15=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H15&lt;&gt;"",$H15,IF($B15=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13"/>
@@ -4086,6 +4239,10 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
+      <c r="J16" s="5" t="str">
+        <f aca="false">IF(OR($A16="",AND($B16&lt;&gt;Paramètres!$B$4,$B16&lt;&gt;Paramètres!$B$5)),"",IF(IF($B16=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H16&lt;&gt;"",$H16,IF($B16=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13"/>
@@ -4100,6 +4257,10 @@
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
+      <c r="J17" s="5" t="str">
+        <f aca="false">IF(OR($A17="",AND($B17&lt;&gt;Paramètres!$B$4,$B17&lt;&gt;Paramètres!$B$5)),"",IF(IF($B17=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H17&lt;&gt;"",$H17,IF($B17=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13"/>
@@ -4114,6 +4275,10 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
+      <c r="J18" s="5" t="str">
+        <f aca="false">IF(OR($A18="",AND($B18&lt;&gt;Paramètres!$B$4,$B18&lt;&gt;Paramètres!$B$5)),"",IF(IF($B18=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H18&lt;&gt;"",$H18,IF($B18=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13"/>
@@ -4128,6 +4293,10 @@
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
+      <c r="J19" s="5" t="str">
+        <f aca="false">IF(OR($A19="",AND($B19&lt;&gt;Paramètres!$B$4,$B19&lt;&gt;Paramètres!$B$5)),"",IF(IF($B19=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H19&lt;&gt;"",$H19,IF($B19=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13"/>
@@ -4142,6 +4311,10 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
+      <c r="J20" s="5" t="str">
+        <f aca="false">IF(OR($A20="",AND($B20&lt;&gt;Paramètres!$B$4,$B20&lt;&gt;Paramètres!$B$5)),"",IF(IF($B20=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H20&lt;&gt;"",$H20,IF($B20=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13"/>
@@ -4156,6 +4329,10 @@
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
+      <c r="J21" s="5" t="str">
+        <f aca="false">IF(OR($A21="",AND($B21&lt;&gt;Paramètres!$B$4,$B21&lt;&gt;Paramètres!$B$5)),"",IF(IF($B21=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H21&lt;&gt;"",$H21,IF($B21=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13"/>
@@ -4170,6 +4347,10 @@
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
+      <c r="J22" s="5" t="str">
+        <f aca="false">IF(OR($A22="",AND($B22&lt;&gt;Paramètres!$B$4,$B22&lt;&gt;Paramètres!$B$5)),"",IF(IF($B22=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H22&lt;&gt;"",$H22,IF($B22=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13"/>
@@ -4184,6 +4365,10 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
+      <c r="J23" s="5" t="str">
+        <f aca="false">IF(OR($A23="",AND($B23&lt;&gt;Paramètres!$B$4,$B23&lt;&gt;Paramètres!$B$5)),"",IF(IF($B23=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H23&lt;&gt;"",$H23,IF($B23=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
@@ -4198,6 +4383,10 @@
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
+      <c r="J24" s="5" t="str">
+        <f aca="false">IF(OR($A24="",AND($B24&lt;&gt;Paramètres!$B$4,$B24&lt;&gt;Paramètres!$B$5)),"",IF(IF($B24=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H24&lt;&gt;"",$H24,IF($B24=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13"/>
@@ -4212,6 +4401,10 @@
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
+      <c r="J25" s="5" t="str">
+        <f aca="false">IF(OR($A25="",AND($B25&lt;&gt;Paramètres!$B$4,$B25&lt;&gt;Paramètres!$B$5)),"",IF(IF($B25=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H25&lt;&gt;"",$H25,IF($B25=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13"/>
@@ -4226,6 +4419,10 @@
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
+      <c r="J26" s="5" t="str">
+        <f aca="false">IF(OR($A26="",AND($B26&lt;&gt;Paramètres!$B$4,$B26&lt;&gt;Paramètres!$B$5)),"",IF(IF($B26=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H26&lt;&gt;"",$H26,IF($B26=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13"/>
@@ -4240,6 +4437,10 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
+      <c r="J27" s="5" t="str">
+        <f aca="false">IF(OR($A27="",AND($B27&lt;&gt;Paramètres!$B$4,$B27&lt;&gt;Paramètres!$B$5)),"",IF(IF($B27=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H27&lt;&gt;"",$H27,IF($B27=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13"/>
@@ -4254,6 +4455,10 @@
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
+      <c r="J28" s="5" t="str">
+        <f aca="false">IF(OR($A28="",AND($B28&lt;&gt;Paramètres!$B$4,$B28&lt;&gt;Paramètres!$B$5)),"",IF(IF($B28=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H28&lt;&gt;"",$H28,IF($B28=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13"/>
@@ -4268,6 +4473,10 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
+      <c r="J29" s="5" t="str">
+        <f aca="false">IF(OR($A29="",AND($B29&lt;&gt;Paramètres!$B$4,$B29&lt;&gt;Paramètres!$B$5)),"",IF(IF($B29=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H29&lt;&gt;"",$H29,IF($B29=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13"/>
@@ -4282,6 +4491,10 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
+      <c r="J30" s="5" t="str">
+        <f aca="false">IF(OR($A30="",AND($B30&lt;&gt;Paramètres!$B$4,$B30&lt;&gt;Paramètres!$B$5)),"",IF(IF($B30=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H30&lt;&gt;"",$H30,IF($B30=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13"/>
@@ -4296,6 +4509,10 @@
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
+      <c r="J31" s="5" t="str">
+        <f aca="false">IF(OR($A31="",AND($B31&lt;&gt;Paramètres!$B$4,$B31&lt;&gt;Paramètres!$B$5)),"",IF(IF($B31=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H31&lt;&gt;"",$H31,IF($B31=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13"/>
@@ -4310,6 +4527,10 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
+      <c r="J32" s="5" t="str">
+        <f aca="false">IF(OR($A32="",AND($B32&lt;&gt;Paramètres!$B$4,$B32&lt;&gt;Paramètres!$B$5)),"",IF(IF($B32=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H32&lt;&gt;"",$H32,IF($B32=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13"/>
@@ -4324,6 +4545,10 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
+      <c r="J33" s="5" t="str">
+        <f aca="false">IF(OR($A33="",AND($B33&lt;&gt;Paramètres!$B$4,$B33&lt;&gt;Paramètres!$B$5)),"",IF(IF($B33=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H33&lt;&gt;"",$H33,IF($B33=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13"/>
@@ -4338,6 +4563,10 @@
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
+      <c r="J34" s="5" t="str">
+        <f aca="false">IF(OR($A34="",AND($B34&lt;&gt;Paramètres!$B$4,$B34&lt;&gt;Paramètres!$B$5)),"",IF(IF($B34=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H34&lt;&gt;"",$H34,IF($B34=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13"/>
@@ -4352,6 +4581,10 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
+      <c r="J35" s="5" t="str">
+        <f aca="false">IF(OR($A35="",AND($B35&lt;&gt;Paramètres!$B$4,$B35&lt;&gt;Paramètres!$B$5)),"",IF(IF($B35=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H35&lt;&gt;"",$H35,IF($B35=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13"/>
@@ -4366,6 +4599,10 @@
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
+      <c r="J36" s="5" t="str">
+        <f aca="false">IF(OR($A36="",AND($B36&lt;&gt;Paramètres!$B$4,$B36&lt;&gt;Paramètres!$B$5)),"",IF(IF($B36=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H36&lt;&gt;"",$H36,IF($B36=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13"/>
@@ -4380,6 +4617,10 @@
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
+      <c r="J37" s="5" t="str">
+        <f aca="false">IF(OR($A37="",AND($B37&lt;&gt;Paramètres!$B$4,$B37&lt;&gt;Paramètres!$B$5)),"",IF(IF($B37=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H37&lt;&gt;"",$H37,IF($B37=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13"/>
@@ -4394,6 +4635,10 @@
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
+      <c r="J38" s="5" t="str">
+        <f aca="false">IF(OR($A38="",AND($B38&lt;&gt;Paramètres!$B$4,$B38&lt;&gt;Paramètres!$B$5)),"",IF(IF($B38=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H38&lt;&gt;"",$H38,IF($B38=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13"/>
@@ -4408,6 +4653,10 @@
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
+      <c r="J39" s="5" t="str">
+        <f aca="false">IF(OR($A39="",AND($B39&lt;&gt;Paramètres!$B$4,$B39&lt;&gt;Paramètres!$B$5)),"",IF(IF($B39=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H39&lt;&gt;"",$H39,IF($B39=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13"/>
@@ -4422,6 +4671,10 @@
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
+      <c r="J40" s="5" t="str">
+        <f aca="false">IF(OR($A40="",AND($B40&lt;&gt;Paramètres!$B$4,$B40&lt;&gt;Paramètres!$B$5)),"",IF(IF($B40=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H40&lt;&gt;"",$H40,IF($B40=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13"/>
@@ -4436,6 +4689,10 @@
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
+      <c r="J41" s="5" t="str">
+        <f aca="false">IF(OR($A41="",AND($B41&lt;&gt;Paramètres!$B$4,$B41&lt;&gt;Paramètres!$B$5)),"",IF(IF($B41=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H41&lt;&gt;"",$H41,IF($B41=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13"/>
@@ -4450,6 +4707,10 @@
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
+      <c r="J42" s="5" t="str">
+        <f aca="false">IF(OR($A42="",AND($B42&lt;&gt;Paramètres!$B$4,$B42&lt;&gt;Paramètres!$B$5)),"",IF(IF($B42=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H42&lt;&gt;"",$H42,IF($B42=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13"/>
@@ -4464,6 +4725,10 @@
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
+      <c r="J43" s="5" t="str">
+        <f aca="false">IF(OR($A43="",AND($B43&lt;&gt;Paramètres!$B$4,$B43&lt;&gt;Paramètres!$B$5)),"",IF(IF($B43=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H43&lt;&gt;"",$H43,IF($B43=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13"/>
@@ -4478,10 +4743,14 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
+      <c r="J44" s="5" t="str">
+        <f aca="false">IF(OR($A44="",AND($B44&lt;&gt;Paramètres!$B$4,$B44&lt;&gt;Paramètres!$B$5)),"",IF(IF($B44=Paramètres!$B$4,Paramètres!$B$15,Paramètres!$C$15)="Forfait","",IF($H44&lt;&gt;"",$H44,IF($B44=Paramètres!$B$4,Paramètres!$B$6,Paramètres!$B$7))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F45" s="9" t="n">
         <f aca="false">SUM(F5:F44)</f>
@@ -4533,17 +4802,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">SUMIFS(Charges!$F$5:$F$54,Charges!$B$5:$B$54,"Imprévus")</f>
@@ -4552,13 +4821,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0</v>
@@ -4566,7 +4835,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="true">IF(B5="",0,MAX(0,(YEAR(TODAY())-YEAR(B5))*12+MONTH(TODAY())-MONTH(B5)+1))</f>
@@ -4575,7 +4844,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">B6+B4*B7</f>
@@ -4584,7 +4853,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">SUM(C13:C62)</f>
@@ -4593,7 +4862,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">B8-B9</f>
@@ -4602,21 +4871,21 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
